--- a/output/Data and Chart Outputs/dominican_republic_gas.xlsx
+++ b/output/Data and Chart Outputs/dominican_republic_gas.xlsx
@@ -210,6 +210,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>

--- a/output/Data and Chart Outputs/dominican_republic_gas.xlsx
+++ b/output/Data and Chart Outputs/dominican_republic_gas.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -155,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Dominican Republic gas use (gas burned for power, SIE) (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -638,7 +640,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -653,7 +654,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -720,7 +720,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -728,7 +728,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -736,7 +736,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -744,7 +744,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -752,7 +752,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -760,7 +760,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -768,7 +768,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -776,7 +776,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -784,7 +784,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -792,7 +792,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -800,7 +800,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -808,7 +808,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -816,7 +816,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -824,7 +824,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -832,7 +832,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -840,7 +840,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -848,7 +848,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -856,7 +856,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -864,7 +864,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -872,7 +872,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -880,7 +880,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -888,7 +888,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -896,7 +896,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -904,7 +904,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -912,7 +912,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -920,7 +920,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -928,7 +928,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -936,7 +936,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -944,7 +944,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -952,7 +952,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -960,7 +960,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -968,7 +968,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -976,7 +976,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -984,7 +984,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -992,7 +992,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1000,7 +1000,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1008,7 +1008,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1016,7 +1016,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1024,7 +1024,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1032,7 +1032,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1040,7 +1040,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1048,7 +1048,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -1056,7 +1056,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -1064,7 +1064,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -1072,7 +1072,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -1080,7 +1080,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -1088,7 +1088,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -1096,7 +1096,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -1104,7 +1104,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -1112,7 +1112,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -1120,7 +1120,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -1128,7 +1128,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -1136,7 +1136,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -1144,7 +1144,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -1152,7 +1152,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -1160,7 +1160,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -1168,7 +1168,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -1176,7 +1176,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -1184,7 +1184,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -1192,7 +1192,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -1200,7 +1200,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -1208,7 +1208,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -1216,7 +1216,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -1224,7 +1224,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">

--- a/output/Data and Chart Outputs/dominican_republic_gas.xlsx
+++ b/output/Data and Chart Outputs/dominican_republic_gas.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,13 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,7 +156,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Dominican Republic gas use (gas burned for power, SIE) (to May/26)</a:t>
+              <a:t>Dominican Republic gas use (gas burned for power, SIE) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -187,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$66</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$66</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -640,6 +639,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -650,10 +650,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jan-2021 to May-2026 (65 months). Natural gas burned to generate electricity for the SENI wholesale market (AES Andres, Los Mina, Estrella del Mar, Energia Natural del Caribe / Manzanillo, converted engines and steam units). All Dominican gas is imported LNG; gas sold to industry and vehicles (GNV) is not included and is not published monthly. SIE updates the file every few months.</t>
+          <t>Jan-2021 to Sep-2026 (69 months). Natural gas burned to generate electricity for the SENI wholesale market (AES Andres, Los Mina, Estrella del Mar, Energia Natural del Caribe / Manzanillo, converted engines and steam units). All Dominican gas is imported LNG; gas sold to industry and vehicles (GNV) is not included and is not published monthly. SIE updates the file every few months.</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -671,7 +672,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>File read this run: https://sie.gob.do/wp-content/uploads/2025/07/Copia-de-Consumo-Combustible_Mensual_2026-xls-1.xlsx</t>
+          <t>File read this run: https://sie.gob.do/wp-content/uploads/2025/07/Consumo-combustible-mensual-2026-1.xlsx</t>
         </is>
       </c>
     </row>
@@ -693,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -712,7 +713,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -720,7 +721,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -728,7 +729,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -736,7 +737,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -744,7 +745,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -752,7 +753,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -760,7 +761,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -768,7 +769,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -776,7 +777,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -784,7 +785,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -792,7 +793,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -800,7 +801,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -808,7 +809,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -816,7 +817,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -824,7 +825,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -832,7 +833,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -840,7 +841,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -848,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -856,7 +857,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -864,7 +865,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -872,7 +873,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -880,7 +881,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -888,7 +889,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -896,7 +897,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -904,7 +905,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -912,7 +913,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -920,7 +921,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -928,7 +929,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -936,7 +937,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -944,7 +945,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -952,7 +953,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -960,7 +961,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -968,7 +969,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -976,7 +977,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -984,7 +985,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -992,7 +993,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1000,7 +1001,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1008,7 +1009,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1016,7 +1017,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1024,7 +1025,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1032,7 +1033,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1040,7 +1041,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1048,7 +1049,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -1056,7 +1057,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -1064,7 +1065,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -1072,7 +1073,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -1080,7 +1081,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -1088,7 +1089,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -1096,7 +1097,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -1104,7 +1105,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -1112,7 +1113,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -1120,7 +1121,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -1128,7 +1129,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -1136,7 +1137,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -1144,7 +1145,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -1152,7 +1153,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -1160,7 +1161,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -1168,7 +1169,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -1176,7 +1177,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -1184,7 +1185,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -1192,7 +1193,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -1200,7 +1201,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -1208,7 +1209,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -1216,7 +1217,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -1224,11 +1225,43 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
         <v>6.7588</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7.4378</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.0778</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.2389</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.4447</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2778,6 +2811,98 @@
         <v>188.539</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7.4378</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8171.495</v>
+      </c>
+      <c r="D67" t="n">
+        <v>272383</v>
+      </c>
+      <c r="E67" t="n">
+        <v>341.329</v>
+      </c>
+      <c r="F67" t="n">
+        <v>17901.596</v>
+      </c>
+      <c r="G67" t="n">
+        <v>234.974</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.0778</v>
+      </c>
+      <c r="C68" t="n">
+        <v>8035.171</v>
+      </c>
+      <c r="D68" t="n">
+        <v>259199</v>
+      </c>
+      <c r="E68" t="n">
+        <v>237.826</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22722.205</v>
+      </c>
+      <c r="G68" t="n">
+        <v>270.096</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.2389</v>
+      </c>
+      <c r="C69" t="n">
+        <v>8218.078</v>
+      </c>
+      <c r="D69" t="n">
+        <v>265099</v>
+      </c>
+      <c r="E69" t="n">
+        <v>283.593</v>
+      </c>
+      <c r="F69" t="n">
+        <v>27056.658</v>
+      </c>
+      <c r="G69" t="n">
+        <v>264.604</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.4447</v>
+      </c>
+      <c r="C70" t="n">
+        <v>8179</v>
+      </c>
+      <c r="D70" t="n">
+        <v>272633</v>
+      </c>
+      <c r="E70" t="n">
+        <v>235</v>
+      </c>
+      <c r="F70" t="n">
+        <v>28586</v>
+      </c>
+      <c r="G70" t="n">
+        <v>243</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
